--- a/export_tables.xlsx
+++ b/export_tables.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,93 +528,6 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>45.612562</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EDFA_11_1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EDFA 1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>edfa</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>56.085655</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>40.143547</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>EDFA_11_2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EDFA 2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>edfa</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>55.550915</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>42.608643</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EDFA_11_3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EDFA 3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>edfa</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>55.461766</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>45.338898</t>
         </is>
       </c>
     </row>
@@ -629,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,7 +590,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11_S1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -687,12 +600,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EDFA_11_1</t>
+          <t>NODE_B</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>500.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -712,133 +625,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>маршрут</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>11_S2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>EDFA_11_1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EDFA_11_2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>179.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>G.652</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.220</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>маршрут</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>11_S3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EDFA_11_2</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EDFA_11_3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>179.00</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>G.652</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.220</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>маршрут</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>11_S4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EDFA_11_3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>NODE_B</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>50.78</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>G.652</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.220</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>маршрут</t>
+          <t>прямая</t>
         </is>
       </c>
     </row>
@@ -853,7 +640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -886,7 +673,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11_S1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -901,7 +688,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,7 +700,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11_S1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -923,24 +710,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>500.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.300</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Узел EDFA_11_1</t>
+          <t>Узел NODE_B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11_S1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -967,7 +754,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11_S1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -994,7 +781,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11_S1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1021,7 +808,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11_S1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1048,7 +835,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11_S1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1075,7 +862,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11_S1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1102,7 +889,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11_S1</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1129,61 +916,61 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11_S2</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Коннектор</t>
+          <t>Сварка</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>200.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Узел EDFA_11_1</t>
+          <t>Стык 8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11_S2</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Коннектор</t>
+          <t>Сварка</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>225.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Узел EDFA_11_2</t>
+          <t>Стык 9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11_S2</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1193,7 +980,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>250.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1203,14 +990,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Стык 1</t>
+          <t>Стык 10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11_S2</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1220,7 +1007,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>275.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1230,14 +1017,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Стык 2</t>
+          <t>Стык 11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11_S2</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1247,7 +1034,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>75.00</t>
+          <t>300.00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1257,14 +1044,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Стык 3</t>
+          <t>Стык 12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11_S2</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1274,7 +1061,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>325.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1284,14 +1071,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Стык 4</t>
+          <t>Стык 13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11_S2</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1301,7 +1088,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>125.00</t>
+          <t>350.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1311,14 +1098,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Стык 5</t>
+          <t>Стык 14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11_S2</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1328,7 +1115,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>375.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1338,14 +1125,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Стык 6</t>
+          <t>Стык 15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>11_S2</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1355,7 +1142,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>175.00</t>
+          <t>400.00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1365,68 +1152,68 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Стык 7</t>
+          <t>Стык 16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>11_S3</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Коннектор</t>
+          <t>Сварка</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>425.00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Узел EDFA_11_2</t>
+          <t>Стык 17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11_S3</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Коннектор</t>
+          <t>Сварка</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>179.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.000</t>
+          <t>0.020</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Узел EDFA_11_3</t>
+          <t>Стык 18</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>11_S3</t>
+          <t>213</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1436,7 +1223,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>475.00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1446,277 +1233,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Стык 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>11_S3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Сварка</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Стык 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>11_S3</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Сварка</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Стык 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>11_S3</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Сварка</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Стык 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>11_S3</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Сварка</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Стык 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>11_S3</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Сварка</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Стык 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>11_S3</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Сварка</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Стык 7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>11_S4</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Коннектор</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>0.300</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Узел EDFA_11_3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>11_S4</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Коннектор</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>50.78</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>0.300</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Узел NODE_B</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>11_S4</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Сварка</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>25.00</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Стык 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>11_S4</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Сварка</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>0.020</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Стык 2</t>
+          <t>Стык 19</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1316,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NODE_A -&gt; EDFA_11_1 -&gt; EDFA_11_2 -&gt; EDFA_11_3 -&gt; NODE_B</t>
+          <t>NODE_A -&gt; NODE_B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1814,17 +1331,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>130.37</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2032,7 +1549,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NODE_A -&gt; EDFA_11_1 -&gt; EDFA_11_2 -&gt; EDFA_11_3 -&gt; NODE_B</t>
+          <t>NODE_A -&gt; NODE_B</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2042,7 +1559,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>587.8</t>
+          <t>500</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2072,22 +1589,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>130.4</t>
+          <t>111</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -2097,7 +1614,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -2112,17 +1629,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>167</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -2137,7 +1654,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -2147,32 +1664,32 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
           <t>OK</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>FAIL</t>
         </is>
       </c>
     </row>
